--- a/LF/PreTAS/Zambia/zm_lf_ems_2510_3_fts.xlsx
+++ b/LF/PreTAS/Zambia/zm_lf_ems_2510_3_fts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\LF\PreTAS\Zambia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C49D9B0-B1F5-4298-A4D8-EC56DC75B273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FE9762-AE6D-4222-A635-411A360E2C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
